--- a/data/trans_orig/P1414-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1414-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de fibromialgia en 2012</t>
+          <t>Población con diagnóstico de fibromialgia en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8571</t>
+          <t>8541</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>37405</t>
+          <t>38040</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>67602</t>
+          <t>67879</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>41543</t>
+          <t>41379</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>72702</t>
+          <t>71633</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>966072</t>
+          <t>966102</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>973633</t>
+          <t>973637</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1269228</t>
+          <t>1268951</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1299425</t>
+          <t>1298790</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2238771</t>
+          <t>2239840</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2269930</t>
+          <t>2270094</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,21%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1047</t>
+          <t>1078</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9816</t>
+          <t>10395</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25220</t>
+          <t>24313</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>49331</t>
+          <t>49599</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28483</t>
+          <t>29458</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>54411</t>
+          <t>54487</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1954141</t>
+          <t>1953562</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1962910</t>
+          <t>1962879</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1705261</t>
+          <t>1704993</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1729372</t>
+          <t>1730279</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3664138</t>
+          <t>3664062</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3690066</t>
+          <t>3689091</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,21%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2104</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1940</t>
+          <t>1652</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14783</t>
+          <t>14983</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1964</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14016</t>
+          <t>13380</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>479077</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>481181</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>443848</t>
+          <t>443648</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>456691</t>
+          <t>456979</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>925797</t>
+          <t>926433</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>937849</t>
+          <t>938805</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,89%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3140</t>
+          <t>3199</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15423</t>
+          <t>14768</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>74658</t>
+          <t>74460</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>113309</t>
+          <t>114168</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>81535</t>
+          <t>82405</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>119863</t>
+          <t>121781</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3404359</t>
+          <t>3405014</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3416642</t>
+          <t>3416583</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3436744</t>
+          <t>3435885</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3475395</t>
+          <t>3475593</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6849972</t>
+          <t>6848054</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6888300</t>
+          <t>6887430</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,82%</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de fibromialgia en 2016</t>
+          <t>Población con diagnóstico de fibromialgia en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4959</t>
+          <t>4927</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2355,7 +2355,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>38310</t>
+          <t>36981</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>66037</t>
+          <t>65971</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2385,12 +2385,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>38838</t>
+          <t>38733</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>68098</t>
+          <t>68012</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2420,7 +2420,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -2448,7 +2448,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>749388</t>
+          <t>749420</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>928623</t>
+          <t>928689</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>956350</t>
+          <t>957679</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1680909</t>
+          <t>1680995</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1710169</t>
+          <t>1710274</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,79%</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5252</t>
+          <t>5268</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18798</t>
+          <t>18491</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2698,7 +2698,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>50685</t>
+          <t>51354</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>83473</t>
+          <t>83869</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>60029</t>
+          <t>60143</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>96534</t>
+          <t>95499</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2057587</t>
+          <t>2057894</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2071133</t>
+          <t>2071117</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1904827</t>
+          <t>1904431</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1937615</t>
+          <t>1936946</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3968151</t>
+          <t>3969186</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4004656</t>
+          <t>4004542</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8875</t>
+          <t>8645</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4155</t>
+          <t>4152</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15973</t>
+          <t>16224</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5475</t>
+          <t>5664</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19623</t>
+          <t>20786</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -3134,7 +3134,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>538011</t>
+          <t>538241</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>533167</t>
+          <t>532916</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>544985</t>
+          <t>544988</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1076404</t>
+          <t>1075241</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1090552</t>
+          <t>1090363</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7266</t>
+          <t>7833</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23307</t>
+          <t>23622</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>104436</t>
+          <t>104248</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>151715</t>
+          <t>147360</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>114326</t>
+          <t>117917</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>164940</t>
+          <t>165465</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3354311</t>
+          <t>3353996</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3370352</t>
+          <t>3369785</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3380385</t>
+          <t>3384740</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3427664</t>
+          <t>3427852</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6744778</t>
+          <t>6744253</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6795392</t>
+          <t>6791801</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,29%</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de fibromialgia en 2023</t>
+          <t>Población con diagnóstico de fibromialgia en 2023 (tasa de respuesta: 99,61%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3938,12 +3938,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>1534</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12982</t>
+          <t>12549</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>45262</t>
+          <t>45312</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>66069</t>
+          <t>68140</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>49916</t>
+          <t>50465</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>73881</t>
+          <t>73604</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4023,12 +4023,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,84%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>497867</t>
+          <t>498300</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>509372</t>
+          <t>509315</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>682976</t>
+          <t>680905</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>703783</t>
+          <t>703733</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1186013</t>
+          <t>1186290</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1209978</t>
+          <t>1209429</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>95,99%</t>
         </is>
       </c>
     </row>
@@ -4281,12 +4281,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2844</t>
+          <t>3110</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13764</t>
+          <t>14074</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4296,12 +4296,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4316,12 +4316,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>50699</t>
+          <t>49923</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>86914</t>
+          <t>85380</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4331,12 +4331,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>59641</t>
+          <t>58461</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>94117</t>
+          <t>92274</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -4394,12 +4394,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2274358</t>
+          <t>2274048</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2285278</t>
+          <t>2285012</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,88%</t>
+          <t>99,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2142216</t>
+          <t>2143750</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2178431</t>
+          <t>2179207</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4423135</t>
+          <t>4424978</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4457611</t>
+          <t>4458791</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,71%</t>
         </is>
       </c>
     </row>
@@ -4624,12 +4624,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>574</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6813</t>
+          <t>6852</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4644,7 +4644,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4659,12 +4659,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8973</t>
+          <t>8754</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22323</t>
+          <t>21102</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4694,12 +4694,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9814</t>
+          <t>10108</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23727</t>
+          <t>23204</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4709,12 +4709,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -4737,12 +4737,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>639229</t>
+          <t>639190</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>645460</t>
+          <t>645468</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>637497</t>
+          <t>638718</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>650847</t>
+          <t>651066</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1282135</t>
+          <t>1282658</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1296048</t>
+          <t>1295754</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4822,12 +4822,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,23%</t>
         </is>
       </c>
     </row>
@@ -4967,12 +4967,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8093</t>
+          <t>7975</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24755</t>
+          <t>24661</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5002,12 +5002,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>110552</t>
+          <t>114264</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>159525</t>
+          <t>162308</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>128344</t>
+          <t>129263</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>175644</t>
+          <t>176942</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5052,12 +5052,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -5080,12 +5080,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3420258</t>
+          <t>3420352</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3436920</t>
+          <t>3437038</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5115,12 +5115,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3478470</t>
+          <t>3475687</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3527443</t>
+          <t>3523731</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5150,12 +5150,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6907364</t>
+          <t>6906066</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6954664</t>
+          <t>6953745</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5165,12 +5165,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,18%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1414-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1414-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1006</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8541</t>
+          <t>9094</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>38040</t>
+          <t>38328</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>67879</t>
+          <t>66986</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>41379</t>
+          <t>41657</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>71633</t>
+          <t>71955</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>966102</t>
+          <t>965549</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>973637</t>
+          <t>973633</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1268951</t>
+          <t>1269844</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1298790</t>
+          <t>1298502</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2239840</t>
+          <t>2239518</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2270094</t>
+          <t>2269816</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,2%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1078</t>
+          <t>1140</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10395</t>
+          <t>10347</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24313</t>
+          <t>24944</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>49599</t>
+          <t>49742</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>29458</t>
+          <t>29233</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>54487</t>
+          <t>54561</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1953562</t>
+          <t>1953610</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1962879</t>
+          <t>1962817</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,95%</t>
+          <t>99,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1704993</t>
+          <t>1704850</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1730279</t>
+          <t>1729648</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3664062</t>
+          <t>3663988</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3689091</t>
+          <t>3689316</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1652</t>
+          <t>1965</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14983</t>
+          <t>15421</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>1811</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13380</t>
+          <t>15027</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>443648</t>
+          <t>443210</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>456979</t>
+          <t>456666</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>926433</t>
+          <t>924786</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>938805</t>
+          <t>938002</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,89%</t>
+          <t>99,81%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3199</t>
+          <t>3149</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14768</t>
+          <t>14302</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>74460</t>
+          <t>74810</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>114168</t>
+          <t>113815</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>82405</t>
+          <t>82529</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>121781</t>
+          <t>120909</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3405014</t>
+          <t>3405480</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3416583</t>
+          <t>3416633</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3435885</t>
+          <t>3436238</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3475593</t>
+          <t>3475243</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6848054</t>
+          <t>6848926</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6887430</t>
+          <t>6887306</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4927</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2355,7 +2355,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>36981</t>
+          <t>38431</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>65971</t>
+          <t>65985</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>38733</t>
+          <t>38396</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>68012</t>
+          <t>68237</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -2448,7 +2448,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>749420</t>
+          <t>749368</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>928689</t>
+          <t>928675</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>957679</t>
+          <t>956229</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1680995</t>
+          <t>1680770</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1710274</t>
+          <t>1710611</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,8%</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5268</t>
+          <t>6061</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18491</t>
+          <t>19799</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>51354</t>
+          <t>49372</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>83869</t>
+          <t>82857</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>60143</t>
+          <t>60523</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>95499</t>
+          <t>95475</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2057894</t>
+          <t>2056586</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2071117</t>
+          <t>2070324</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1904431</t>
+          <t>1905443</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1936946</t>
+          <t>1938928</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3969186</t>
+          <t>3969210</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4004542</t>
+          <t>4004162</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,51%</t>
         </is>
       </c>
     </row>
@@ -3026,7 +3026,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8645</t>
+          <t>8400</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4152</t>
+          <t>4146</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16224</t>
+          <t>16522</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5664</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20786</t>
+          <t>19728</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -3134,7 +3134,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>538241</t>
+          <t>538486</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>532916</t>
+          <t>532618</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>544988</t>
+          <t>544994</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1075241</t>
+          <t>1076299</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1090363</t>
+          <t>1090625</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,51%</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7833</t>
+          <t>7330</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23622</t>
+          <t>22936</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>104248</t>
+          <t>104497</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>147360</t>
+          <t>148655</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>117917</t>
+          <t>116482</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>165465</t>
+          <t>165345</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3353996</t>
+          <t>3354682</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3369785</t>
+          <t>3370288</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3384740</t>
+          <t>3383445</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3427852</t>
+          <t>3427603</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6744253</t>
+          <t>6744373</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6791801</t>
+          <t>6793236</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,31%</t>
         </is>
       </c>
     </row>
@@ -3933,32 +3933,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4836</t>
+          <t>4977</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1534</t>
+          <t>1436</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12549</t>
+          <t>12678</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3968,32 +3968,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>55688</t>
+          <t>62314</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>45312</t>
+          <t>50384</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>68140</t>
+          <t>74576</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4003,32 +4003,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>60524</t>
+          <t>67291</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>50465</t>
+          <t>55554</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>73604</t>
+          <t>82424</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,93%</t>
         </is>
       </c>
     </row>
@@ -4046,32 +4046,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>506013</t>
+          <t>569260</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>498300</t>
+          <t>561559</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>509315</t>
+          <t>572801</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4081,32 +4081,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>693357</t>
+          <t>754123</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>680905</t>
+          <t>741861</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>703733</t>
+          <t>766053</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4116,32 +4116,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1199370</t>
+          <t>1323384</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1186290</t>
+          <t>1308251</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1209429</t>
+          <t>1335121</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>96,01%</t>
         </is>
       </c>
     </row>
@@ -4159,17 +4159,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>510849</t>
+          <t>574237</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>510849</t>
+          <t>574237</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>510849</t>
+          <t>574237</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4194,17 +4194,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>749045</t>
+          <t>816437</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>749045</t>
+          <t>816437</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>749045</t>
+          <t>816437</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4229,17 +4229,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1259894</t>
+          <t>1390675</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1259894</t>
+          <t>1390675</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1259894</t>
+          <t>1390675</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4276,32 +4276,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7096</t>
+          <t>7416</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3110</t>
+          <t>3464</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14074</t>
+          <t>14024</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4311,32 +4311,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>70009</t>
+          <t>77589</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>49923</t>
+          <t>64198</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>85380</t>
+          <t>91108</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4346,32 +4346,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>77106</t>
+          <t>85004</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>58461</t>
+          <t>70986</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>92274</t>
+          <t>100993</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -4389,32 +4389,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2281026</t>
+          <t>2220511</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2274048</t>
+          <t>2213903</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2285012</t>
+          <t>2224463</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4424,32 +4424,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2159121</t>
+          <t>2083601</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2143750</t>
+          <t>2070082</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2179207</t>
+          <t>2096992</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4459,32 +4459,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4440146</t>
+          <t>4304113</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4424978</t>
+          <t>4288124</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4458791</t>
+          <t>4318131</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,38%</t>
         </is>
       </c>
     </row>
@@ -4502,17 +4502,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2288122</t>
+          <t>2227927</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2288122</t>
+          <t>2227927</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2288122</t>
+          <t>2227927</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4537,17 +4537,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2229130</t>
+          <t>2161190</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2229130</t>
+          <t>2161190</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2229130</t>
+          <t>2161190</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4572,17 +4572,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4517252</t>
+          <t>4389117</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4517252</t>
+          <t>4389117</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4517252</t>
+          <t>4389117</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4619,32 +4619,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2372</t>
+          <t>2374</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>574</t>
+          <t>578</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6852</t>
+          <t>6912</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4654,32 +4654,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>13324</t>
+          <t>14371</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8754</t>
+          <t>9066</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21102</t>
+          <t>22990</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4689,32 +4689,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>15696</t>
+          <t>16745</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10108</t>
+          <t>10734</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23204</t>
+          <t>26175</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -4732,32 +4732,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>643670</t>
+          <t>708626</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>639190</t>
+          <t>704088</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>645468</t>
+          <t>710422</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,91%</t>
+          <t>99,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4767,32 +4767,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>646496</t>
+          <t>717709</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>638718</t>
+          <t>709090</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>651066</t>
+          <t>723014</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4802,32 +4802,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1290166</t>
+          <t>1426335</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1282658</t>
+          <t>1416905</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1295754</t>
+          <t>1432346</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,26%</t>
         </is>
       </c>
     </row>
@@ -4845,17 +4845,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646042</t>
+          <t>711000</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646042</t>
+          <t>711000</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646042</t>
+          <t>711000</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4880,17 +4880,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>659820</t>
+          <t>732080</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>659820</t>
+          <t>732080</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>659820</t>
+          <t>732080</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4915,17 +4915,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1305862</t>
+          <t>1443080</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1305862</t>
+          <t>1443080</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1305862</t>
+          <t>1443080</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4962,17 +4962,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14305</t>
+          <t>14767</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7975</t>
+          <t>8982</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24661</t>
+          <t>25651</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4997,32 +4997,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>139021</t>
+          <t>154273</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>114264</t>
+          <t>136027</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>162308</t>
+          <t>172249</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5032,32 +5032,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>153325</t>
+          <t>169040</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>129263</t>
+          <t>150529</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>176942</t>
+          <t>190245</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -5075,17 +5075,17 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3430708</t>
+          <t>3498397</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3420352</t>
+          <t>3487513</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3437038</t>
+          <t>3504182</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5110,32 +5110,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3498974</t>
+          <t>3555434</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3475687</t>
+          <t>3537458</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3523731</t>
+          <t>3573680</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5145,32 +5145,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6929683</t>
+          <t>7053832</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6906066</t>
+          <t>7032627</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6953745</t>
+          <t>7072343</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>97,92%</t>
         </is>
       </c>
     </row>
@@ -5188,17 +5188,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3445013</t>
+          <t>3513164</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3445013</t>
+          <t>3513164</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3445013</t>
+          <t>3513164</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5223,17 +5223,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3637995</t>
+          <t>3709707</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3637995</t>
+          <t>3709707</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3637995</t>
+          <t>3709707</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5258,17 +5258,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7083008</t>
+          <t>7222872</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7083008</t>
+          <t>7222872</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7083008</t>
+          <t>7222872</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
